--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
@@ -11,18 +11,20 @@
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$7</definedName>
     <definedName name="Hidden_29">Hidden_2!$A$1:$A$3</definedName>
-    <definedName name="Hidden_323">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_314">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_424">Hidden_4!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
   <si>
     <t>48981</t>
   </si>
@@ -105,6 +107,9 @@
     <t>436376</t>
   </si>
   <si>
+    <t>571934</t>
+  </si>
+  <si>
     <t>436382</t>
   </si>
   <si>
@@ -192,6 +197,9 @@
     <t>Razón social del titular al cual se otorgó el acto jurídico</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fecha de inicio de vigencia del acto jurídico </t>
   </si>
   <si>
@@ -237,7 +245,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -246,45 +254,42 @@
     <t>Departamento  de Recursos Humanos</t>
   </si>
   <si>
-    <t>B74779125D9BCDBF6DBE7AB7A3D897E1</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>14/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
-  </si>
-  <si>
-    <t>9E75CAA1A9826283F8957946F20CA013</t>
+    <t>CCEB2C1EB62C57CFC08858F987625FD4</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>13/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
+  </si>
+  <si>
+    <t>Licencia</t>
+  </si>
+  <si>
+    <t>Contrato</t>
+  </si>
+  <si>
+    <t>Convenio</t>
+  </si>
+  <si>
+    <t>Permiso</t>
+  </si>
+  <si>
+    <t>Concesión</t>
+  </si>
+  <si>
+    <t>Autorización</t>
   </si>
   <si>
     <t>Asignaciones</t>
   </si>
   <si>
-    <t>Licencia</t>
-  </si>
-  <si>
-    <t>Contrato</t>
-  </si>
-  <si>
-    <t>Convenio</t>
-  </si>
-  <si>
-    <t>Permiso</t>
-  </si>
-  <si>
-    <t>Concesión</t>
-  </si>
-  <si>
-    <t>Autorización</t>
-  </si>
-  <si>
     <t>Privado</t>
   </si>
   <si>
@@ -292,6 +297,12 @@
   </si>
   <si>
     <t>Mixto</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Si</t>
@@ -690,10 +701,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -707,29 +718,30 @@
     <col min="12" max="12" width="49.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="49.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="255" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -746,7 +758,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -761,7 +773,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -802,25 +814,25 @@
         <v>6</v>
       </c>
       <c r="O4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="s">
         <v>7</v>
       </c>
       <c r="Q4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" t="s">
         <v>6</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>10</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>9</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>11</v>
-      </c>
-      <c r="U4" t="s">
-        <v>10</v>
       </c>
       <c r="V4" t="s">
         <v>10</v>
@@ -829,25 +841,28 @@
         <v>10</v>
       </c>
       <c r="X4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y4" t="s">
         <v>8</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>10</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>12</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -932,10 +947,13 @@
       <c r="AC5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -965,274 +983,192 @@
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
-    </row>
-    <row r="7" spans="1:29" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="AB8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>78</v>
+      <c r="AD8" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AC6"/>
+    <mergeCell ref="A6:AD6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1240,15 +1176,18 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E197">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J197">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J199">
       <formula1>Hidden_29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X197">
-      <formula1>Hidden_323</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O199">
+      <formula1>Hidden_314</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y199">
+      <formula1>Hidden_424</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1292,7 +1231,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1307,17 +1246,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1332,12 +1271,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
